--- a/Testdata/TestData.xlsx
+++ b/Testdata/TestData.xlsx
@@ -2,39 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Playrwright Automation\Playwright Projects\GHI\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7EC85F-53EF-49CC-8C41-AA29BF665FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0358157-F879-4FB9-99CA-5A54B18C00CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7C865D6D-DE14-4BFA-96E2-236B8223480B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GHI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="32">
+  <si>
+    <t>Sr No</t>
+  </si>
+  <si>
+    <t>QuoteID</t>
+  </si>
   <si>
     <t>Username</t>
   </si>
@@ -42,38 +34,98 @@
     <t>Password</t>
   </si>
   <si>
-    <t>Sr No</t>
+    <t>BusinessType</t>
+  </si>
+  <si>
+    <t>AgentCode</t>
+  </si>
+  <si>
+    <t>BranchName</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>InsuredName</t>
+  </si>
+  <si>
+    <t>GroupType</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>OccupationMaster</t>
+  </si>
+  <si>
+    <t>ProposalBasis</t>
+  </si>
+  <si>
+    <t>EmployeeType</t>
+  </si>
+  <si>
+    <t>PolicyStartDate</t>
+  </si>
+  <si>
+    <t>SumInsuredType</t>
+  </si>
+  <si>
+    <t>Q200000017007</t>
   </si>
   <si>
     <t>salesuser2@commercial.royalsundaram.net</t>
   </si>
   <si>
     <t>889188</t>
+  </si>
+  <si>
+    <t>New Business</t>
+  </si>
+  <si>
+    <t>AG002020</t>
+  </si>
+  <si>
+    <t>Chennai Regional Office</t>
+  </si>
+  <si>
+    <t>AAR</t>
+  </si>
+  <si>
+    <t>Monika</t>
+  </si>
+  <si>
+    <t>Employer-Employee</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>Housewives</t>
+  </si>
+  <si>
+    <t>Named</t>
+  </si>
+  <si>
+    <t>Contractual / Off-Roll</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>Flat Sum Insured for All</t>
+  </si>
+  <si>
+    <t>TestResult</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -96,22 +148,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -419,42 +466,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{203DC8DD-C215-48F9-AC89-7006DF0FA84B}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="2" width="37.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="14.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{6E2EA4DF-F08A-4E9F-8DF4-18313F5D7024}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{39589E3A-1A85-47B5-8FBF-2DC3B3DD79E0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <ignoredErrors>
+    <ignoredError sqref="A2:Q2 A1 C1:Q1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Testdata/TestData.xlsx
+++ b/Testdata/TestData.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:U5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,45 +416,51 @@
         <v>QuoteID</v>
       </c>
       <c r="F1" t="str">
+        <v>ProposalNumber</v>
+      </c>
+      <c r="G1" t="str">
+        <v>PolicyNumber</v>
+      </c>
+      <c r="H1" t="str">
         <v>Username</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Password</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>BusinessType</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>AgentCode</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>BranchName</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>Channel</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>InsuredName</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>GroupType</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>Industry</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
         <v>OccupationMaster</v>
       </c>
-      <c r="P1" t="str">
+      <c r="R1" t="str">
         <v>ProposalBasis</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>EmployeeType</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>PolicyStartDate</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>SumInsuredType</v>
       </c>
     </row>
@@ -469,69 +475,244 @@
         <v>Fail</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">_x001b_[2mexpect(_x001b_[22m_x001b_[31mlocator_x001b_[39m_x001b_[2m)._x001b_[22mtoHaveText_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m)_x001b_[22m failed
-Locator: locator('[class="mb-4 mt-4 text-lg"]')
-Expected: _x001b_[32m"Get a Quick Quote"_x001b_[39m
-Timeout: 5000ms
-Error: element(s) not found
+        <v xml:space="preserve">locator.click: Test timeout of 180000ms exceeded.
 Call log:
-_x001b_[2m  - Expect "toHaveText" locator('[class="mb-4 mt-4 text-lg"]') with timeout 5000ms_x001b_[22m
-_x001b_[2m  - waiting for locator('[class="mb-4 mt-4 text-lg"]')_x001b_[22m
+_x001b_[2m  - waiting for getByRole('button', { name: ' Take Over ' })_x001b_[22m
 </v>
       </c>
       <c r="E2" t="str">
-        <v>Q200000017237</v>
-      </c>
-      <c r="F2" t="str">
+        <v>Q200000017643</v>
+      </c>
+      <c r="H2" t="str">
         <v>salesuser2@commercial.royalsundaram.net</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>889188</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>New Business</v>
       </c>
-      <c r="I2" t="str">
-        <v>AG002020</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
+        <v>AG020227</v>
+      </c>
+      <c r="L2" t="str">
         <v>Chennai Regional Office</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>AAR</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>Monika</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>Employer-Employee</v>
       </c>
-      <c r="N2" t="str">
+      <c r="P2" t="str">
         <v>Information Technology</v>
       </c>
-      <c r="O2" t="str">
+      <c r="Q2" t="str">
         <v>Housewives</v>
       </c>
-      <c r="P2" t="str">
+      <c r="R2" t="str">
         <v>Named</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>Contractual / Off-Roll</v>
       </c>
-      <c r="R2" t="str">
+      <c r="T2" t="str">
         <v>20/10/2026</v>
       </c>
-      <c r="S2" t="str">
+      <c r="U2" t="str">
+        <v>Flat Sum Insured for All</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>No</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="D3" t="str">
+        <v>page.goto: Target page, context or browser has been closed</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Q200000017643</v>
+      </c>
+      <c r="H3" t="str">
+        <v>salesuser2@commercial.royalsundaram.net</v>
+      </c>
+      <c r="I3" t="str">
+        <v>889188</v>
+      </c>
+      <c r="J3" t="str">
+        <v>New Business</v>
+      </c>
+      <c r="K3" t="str">
+        <v>AG020227</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Chennai Regional Office</v>
+      </c>
+      <c r="M3" t="str">
+        <v>AAR</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Monika</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Employer-Employee</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Housewives</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Named</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Contractual / Off-Roll</v>
+      </c>
+      <c r="T3" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Flat Sum Insured for All</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>yes</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="D4" t="str">
+        <v>page.goto: Target page, context or browser has been closed</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Q200000017643</v>
+      </c>
+      <c r="H4" t="str">
+        <v>salesuser2@commercial.royalsundaram.net</v>
+      </c>
+      <c r="I4" t="str">
+        <v>889188</v>
+      </c>
+      <c r="J4" t="str">
+        <v>New Business</v>
+      </c>
+      <c r="K4" t="str">
+        <v>AG020227</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Chennai Regional Office</v>
+      </c>
+      <c r="M4" t="str">
+        <v>AAR</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Monika</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Employer-Employee</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Housewives</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Named</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Contractual / Off-Roll</v>
+      </c>
+      <c r="T4" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Flat Sum Insured for All</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>No</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="D5" t="str">
+        <v>page.goto: Target page, context or browser has been closed</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Q200000017643</v>
+      </c>
+      <c r="H5" t="str">
+        <v>salesuser2@commercial.royalsundaram.net</v>
+      </c>
+      <c r="I5" t="str">
+        <v>889188</v>
+      </c>
+      <c r="J5" t="str">
+        <v>New Business</v>
+      </c>
+      <c r="K5" t="str">
+        <v>AG020227</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Chennai Regional Office</v>
+      </c>
+      <c r="M5" t="str">
+        <v>AAR</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Monika</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Employer-Employee</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Information Technology</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Housewives</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Named</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Contractual / Off-Roll</v>
+      </c>
+      <c r="T5" t="str">
+        <v>20/10/2026</v>
+      </c>
+      <c r="U5" t="str">
         <v>Flat Sum Insured for All</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Testdata/TestData.xlsx
+++ b/Testdata/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Playrwright Automation\Playwright Projects\GHI\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BBF8B6-8ED6-4015-8A76-A0CF5EA3C68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24B3328-5131-4142-A371-AFBC44272455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>Sr No</t>
   </si>
@@ -173,16 +173,84 @@
   </si>
   <si>
     <t>ExistingClient</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>CustomerContactNumber</t>
+  </si>
+  <si>
+    <t>8237370698</t>
+  </si>
+  <si>
+    <t>AddressLine1</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>AddressLine2</t>
+  </si>
+  <si>
+    <t>AddressLine3</t>
+  </si>
+  <si>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>AddressLine4</t>
+  </si>
+  <si>
+    <t>400001</t>
+  </si>
+  <si>
+    <t>HREmail</t>
+  </si>
+  <si>
+    <t>Test123@gmail.com</t>
+  </si>
+  <si>
+    <t>SubChannel</t>
+  </si>
+  <si>
+    <t>SalesRepCode</t>
+  </si>
+  <si>
+    <t>TUWCode</t>
+  </si>
+  <si>
+    <t>UWCode</t>
+  </si>
+  <si>
+    <t>Affinity</t>
+  </si>
+  <si>
+    <t>HR002808</t>
+  </si>
+  <si>
+    <t>TU002741</t>
+  </si>
+  <si>
+    <t>UW002741</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -205,14 +273,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -525,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.3984375" bestFit="1" customWidth="1"/>
@@ -548,9 +619,14 @@
     <col min="19" max="19" width="19" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.69921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.19921875" customWidth="1"/>
+    <col min="30" max="33" width="12.59765625" customWidth="1"/>
+    <col min="34" max="34" width="21.3984375" customWidth="1"/>
+    <col min="35" max="37" width="12.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -632,8 +708,41 @@
       <c r="AA1" t="s">
         <v>49</v>
       </c>
+      <c r="AB1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -705,11 +814,48 @@
       </c>
       <c r="Z2" t="s">
         <v>48</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="AH2" r:id="rId2" xr:uid="{BC855B46-56BF-47E7-9165-51443DAB3CB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
